--- a/Result/profitability/1806.xlsx
+++ b/Result/profitability/1806.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07999999999999997</v>
+        <v>0.05999999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>24.87875</v>
+        <v>24.66125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.39</v>
       </c>
       <c r="M3" t="n">
-        <v>0.10625</v>
+        <v>0.09749999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>26.895</v>
+        <v>26.93375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.16</v>
       </c>
       <c r="M4" t="n">
-        <v>0.115</v>
+        <v>0.1125</v>
       </c>
       <c r="N4" t="n">
-        <v>29.4275</v>
+        <v>29.80125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1075</v>
+        <v>0.10625</v>
       </c>
       <c r="N5" t="n">
-        <v>31.95375</v>
+        <v>31.89875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.11</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08999999999999998</v>
+        <v>0.07374999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>33.36875</v>
+        <v>33.27</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.125</v>
+        <v>0.12125</v>
       </c>
       <c r="N7" t="n">
-        <v>36.18125</v>
+        <v>36.88375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.37</v>
       </c>
       <c r="M8" t="n">
-        <v>0.16375</v>
+        <v>0.18</v>
       </c>
       <c r="N8" t="n">
-        <v>39.78625</v>
+        <v>40.8325</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9356,13 +9356,13 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-45</v>
+        <v>-43</v>
       </c>
       <c r="J71" t="n">
+        <v>15</v>
+      </c>
+      <c r="K71" t="n">
         <v>13</v>
-      </c>
-      <c r="K71" t="n">
-        <v>11</v>
       </c>
       <c r="L71" t="n">
         <v>0.03</v>
@@ -9483,19 +9483,19 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J72" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K72" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L72" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="M72" t="n">
-        <v>0.06749999999999998</v>
+        <v>0.06624999999999998</v>
       </c>
       <c r="N72" t="n">
         <v>26.3125</v>
@@ -9525,10 +9525,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="X72" t="n">
-        <v>4.333333333333334</v>
+        <v>4</v>
       </c>
       <c r="Y72" t="n">
         <v>0.3499999999999979</v>
@@ -9537,10 +9537,10 @@
         <v>0.01403368083400158</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.01999999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.111111111111111</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="AC72" t="n">
         <v>-0.9499999999999993</v>
@@ -9622,7 +9622,7 @@
         <v>0.06</v>
       </c>
       <c r="M73" t="n">
-        <v>0.07499999999999998</v>
+        <v>0.07374999999999998</v>
       </c>
       <c r="N73" t="n">
         <v>24.28875</v>
@@ -9652,10 +9652,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.625</v>
+        <v>-0.6</v>
       </c>
       <c r="Y73" t="n">
         <v>-6.41</v>
@@ -9749,7 +9749,7 @@
         <v>-0.1</v>
       </c>
       <c r="M74" t="n">
-        <v>0.05874999999999997</v>
+        <v>0.05749999999999997</v>
       </c>
       <c r="N74" t="n">
         <v>22.875</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>775</v>
+      </c>
+      <c r="D75" t="n">
+        <v>585</v>
+      </c>
+      <c r="E75" t="n">
+        <v>190</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>39</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>38</v>
+      </c>
+      <c r="K75" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.05999999999999998</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>8.370000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.518908865468072</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.4400000000000013</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.01764234161988776</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
